--- a/timelog.xlsx
+++ b/timelog.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
   <si>
     <t xml:space="preserve">Total hours:</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t xml:space="preserve">Frontin ja bäkin yhdistys</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frontin ja bäkin hiominen</t>
   </si>
 </sst>
 </file>
@@ -293,7 +296,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="11.53"/>
@@ -305,7 +308,7 @@
       </c>
       <c r="B1" s="1" t="n">
         <f aca="false">SUM(D:D)</f>
-        <v>0.815972222222222</v>
+        <v>0.982638888888889</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -516,6 +519,51 @@
       <c r="F12" s="3" t="s">
         <v>15</v>
       </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <f aca="false">C13-B13</f>
+        <v>0.125</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.708333333333333</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <f aca="false">C14-B14</f>
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D15" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
